--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/02062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/02062026.xlsx
@@ -1,118 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">martes, 2 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Marcos
-Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
-*Oración de la mañana*
-Oración de la Mañana
-Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
-Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
-Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
-En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -136,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -482,193 +456,500 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>martes, 2 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Marcos
+Marcos 12, 13-17 En aquel tiempo, los sumos sacerdotes, los escribas y los ancianos le enviaron a Jesús unos fariseos y unos partidarios de Herodes, para hacerle una pregunta capciosa. Se acercaron, pues, a él y le dijeron: “Maestro, sabemos que eres sincero y que no te importa lo que diga la gente, porque no tratas de adular a los hombres, sino que enseñas con toda verdad el camino de Dios. ¿Está permitido o no, pagarle el tributo al César? ¿Se lo damos o no se lo damos?” Jesús, notando su hipocresía, les dijo: “¿Por qué me ponen una trampa? Tráiganme una moneda para que yo la vea”. Se la trajeron y él les preguntó: “¿De quién es la imagen y el nombre que lleva escrito?” Le contestaron: “Del César”. Entonces les respondió Jesús: “Den al César lo que es del César, y a Dios lo que es de Dios”. Y los dejó admirados.
+*Oración de la mañana*
+Oración de la Mañana
+Querido Jesús, guía mi corazón y mi mente para que pueda discernir lo que es tuyo en este mundo. Ayúdame a recordar que todo lo que poseo es un regalo tuyo, y que debo usarlo para honrar y glorificar tu nombre. Enseña mis labios a hablar con sinceridad y verdad, sin buscar la aprobación de los hombres, sino buscando siempre tu verdad.
+Padre amado, te agradezco por el regalo de este nuevo día. Ayúdame a recordar que todo lo que es del mundo, es del mundo, pero lo que es tuyo es tuyo. Que pueda dar al César lo que es del César, pero siempre dar a ti lo que es tuyo. Permíteme vivir este día en gratitud y generosidad, compartiendo tus dones con los demás.
+Oh Espíritu Santo, despierta en mí tu sabiduría y tu entendimiento. Ayúdame a ver más allá de las trampas y las tentaciones de este mundo, para que pueda seguir tu camino en todo lo que hago. Lléname de tu luz y tu gracia, para que pueda ser un reflejo de tu amor en el mundo.
+En la unidad de la Trinidad, en el amor de Dios, y en la comunión del Espíritu Santo, comienzo este día. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>